--- a/data_extactor/batch_10_fa/trimmed/batch_0024_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0024_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | ریاضیات</t>
+          <t>قانون و دولت | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>دانشمندان علوم جوی و فضایی | مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان محیط زیست | دانشمندان و متخصصان محیط زیست و بهداشت | متخصصان علوم سیاسی | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>دانشمندان و کارشناسان علوم جوی و فضا | مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | دانشمندان و پژوهشگران علوم سیاسی | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>تحلیل و تلخیص یافته‌های پژوهشی اقلیمی جهت اطلاع‌رسانی به قانون‌گذاران، نهادهای نظارتی و سایر ذی‌نفعان | تدوین و مشارکت در اجرای برنامه‌های آموزشی و ترویجی در زمینه محیط زیست و تغییر اقلیم | جمع‌آوری و ارزیابی پژوهش‌های مرتبط با تغییر اقلیم از سازمان‌های دولتی و مراکز پژوهشی | تدوین توصیه‌های سیاستی و تقنینی بر اساس اصول، مبانی و فرآیندهای مدیریت تغییر اقلیم | تهیه گزارش‌های پژوهشی، یادداشت‌های سیاستی و خلاصه‌های مدیریتی برای سازمان‌های دولتی و تشکل‌های زیست‌محیطی | ارائه و دفاع از طرح‌های پیشنهادی پژوهشی در حوزه تغییر اقلیم | ارائه مستندات و اطلاعات سیاستی در نشست‌های تخصصی، مراجع دولتی و مجامع عمومی | پیشنهاد سیاست‌های نوآورانه یا بازنگری‌شده در زمینه سوخت‌های فسیلی و پاک، حمل‌ونقل کالا و متغیرهای اقلیمی | ارائه تحلیل‌های تخصصی برای حمایت از خط‌مشی‌های حوزه انرژی‌های تجدیدپذیر، بهره‌وری انرژی و اقلیم | بررسی قوانین و خط‌مشی‌های جاری به‌منظور شناسایی پیامدهای زیست‌محیطی آن‌ها</t>
+          <t>تجزیه و تحلیل و تلخیص یافته‌های پژوهشی مرتبط با اقلیم برای آگاهی‌بخشی به قانون‌گذاران، نهادهای نظارتی یا سایر ذی‌نفعان. | تدوین برنامه‌های آموزشی یا ترویجی در زمینه محیط‌زیست یا تغییر اقلیم، یا مشارکت در تدوین آن‌ها. | گردآوری و بازبینی مطالعات مرتبط با اقلیم از نهادهای دولتی، آزمایشگاه‌های پژوهشی و سایر سازمان‌ها. | ارائه پیشنهادهای قانون‌گذاری مرتبط با تغییر اقلیم یا مدیریت محیط‌زیست، بر پایه سیاست‌ها، اصول، برنامه‌ها، شیوه‌ها و فرایندهای تغییر اقلیم. | تهیه درخواست‌های اعطای اعتبار برای تأمین مالی برنامه‌های مرتبط با تغییر اقلیم، مدیریت محیط‌زیست یا پایداری. | تهیه گزارش‌های مطالعاتی، یادداشت‌ها، خلاصه‌ها، شهادت‌ها یا سایر مواد مکتوب برای آگاهی‌بخشی به نهادهای دولتی یا گروه‌های محیط‌زیستی درباره مسائل محیط‌زیستی، مانند تغییر اقلیم. | ارائه و دفاع از پیشنهادهای پروژه‌های پژوهشی تغییر اقلیم. | ارائه اطلاعات مرتبط با اقلیم در نشست‌های عمومی، دولتی یا سایر نشست‌ها. | ترویج ابتکارهای کاهش تغییر اقلیم نزد نهادهای دولتی یا گروه‌های محیط‌زیستی. | پیشنهاد سیاست‌های جدید یا اصلاح‌شده درباره استفاده از سوخت‌های سنتی و جایگزین، حمل‌ونقل کالا و سایر عوامل مرتبط با اقلیم و تغییر اقلیم. | ارائه پشتیبانی تحلیلی برای خلاصه‌های سیاستی مرتبط با انرژی تجدیدپذیر، بهره‌وری انرژی یا تغییر اقلیم. | پژوهش درباره سیاست‌ها، شیوه‌ها یا رویه‌های مدیریت اقلیم یا محیط‌زیست. | بازبینی سیاست‌ها یا قوانین موجود برای شناسایی پیامدهای محیط‌زیستی آن‌ها. | نگارش گزارش‌ها یا مقالات علمی برای انتقال یافته‌های مطالعات مرتبط با اقلیم.</t>
         </is>
       </c>
     </row>
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | نظارت | علوم پایه | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | نظارت | علوم | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | جغرافیا | ریاضیات | حقوق و مقررات دولتی | مهندسی و فناوری | رایانه و الکترونیک</t>
+          <t>زیست‌شناسی | جغرافیا | ریاضیات | قانون و دولت | مهندسی و فناوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط زیست | دانشمندان و متخصصان محیط زیست و بهداشت | کارشناسان جنگل‌داری | آب‌شناسان و هیدرولوژیست‌ها | دانشمندان علوم خاک و گیاه‌شناسی</t>
+          <t>مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط‌زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کارشناسان جنگل‌داری و جنگل‌بانان | آب‌شناسان و هیدرولوژیست‌ها | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>پیگیری و اخذ مجوزهای قانونی لازم برای اجرای پروژه‌های بهسازی و احیای زیست‌محیطی | جمع‌آوری و تحلیل داده‌ها به‌منظور تعیین وضعیت زیست‌محیطی و نیازهای احیا | انجام ارزیابی‌های اثرات زیست‌محیطی جهت بررسی پیامدهای بوم‌شناختی آلاینده‌ها، فعالیت‌های انسانی و تغییر اقلیم | تهیه مطالعات امکان‌سنجی فنی و ارزیابی اقتصادی پروژه‌های احیای محیط زیست | ارزیابی میدانی سایت‌ها جهت تعیین میزان خسارات و الزامات بهسازی زیستگاه‌ها | مدل‌سازی و شبیه‌سازی زیست‌محیطی با بهره‌گیری از سامانه‌های اطلاعات جغرافیایی GIS | تدوین برنامه‌های جامع مدیریت و احیای زیستگاه‌ها نظیر احیای پوشش گیاهی بومی و مهار گونه‌های مهاجم | تعیین و تدوین راهکارهای جایگزین جبران و کاهش اثرات زیست‌محیطی مطابق مقررات جاری | بازرسی از کارگاه‌های بهسازی زیست‌محیطی جهت حصول اطمینان از انطباق با استانداردهای ایمنی و محیط زیست | برنامه‌ریزی زمان‌بندی و برآورد بودجه پروژه‌های احیای زیست‌محیطی</t>
+          <t>درخواست مجوزهای لازم برای اجرای پروژه‌های پاک‌سازی محیط‌زیستی. | گردآوری و تجزیه و تحلیل داده‌ها برای تعیین شرایط محیط‌زیستی و نیازهای احیا. | انتقال یافته‌های مطالعات محیط‌زیستی یا پیشنهادهای پاک‌سازی محیط‌زیستی به سایر متخصصان احیا. | انجام مطالعات ارزیابی اثرات محیط‌زیستی برای بررسی آثار بوم‌شناختی آلاینده‌ها، بیماری، فعالیت‌های انسانی، طبیعت و تغییر اقلیم. | انجام مطالعات امکان‌سنجی و هزینه‌فایده برای پروژه‌های پاک‌سازی محیط‌زیستی. | انجام ارزیابی‌های سایت برای تأیید یک زیستگاه یا تعیین آسیب محیط‌زیستی و نیازهای احیا. | ترسیم نمودار برای انتقال برنامه‌ریزی پاک‌سازی محیط‌زیستی، با استفاده از سامانه اطلاعات جغرافیایی (GIS)، طراحی به کمک رایانه (CAD) یا سایر نرم‌افزارهای نقشه‌کشی و نمودارسازی. | ساخت مدل‌ها یا شبیه‌سازی‌های محیط‌زیستی، با استفاده از داده‌های سامانه اطلاعات جغرافیایی (GIS) و دانش بوم‌سازگان‌ها یا مناطق بوم‌شناختی خاص. | تدوین برنامه‌های مدیریت یا احیای زیستگاه، مانند احیای درختان بومی و کنترل علف‌های هرز. | تدوین و ابلاغ توصیه‌ها به مالکان زمین برای حفظ یا احیای شرایط محیط‌زیستی. | تدوین برنامه‌های مدیریت یا احیای محیط‌زیست برای محل‌های دارای خطوط انتقال برق، خطوط لوله گاز طبیعی، پالایشگاه سوخت، نیروگاه زمین‌گرمایی، مزرعه بادی یا مزرعه خورشیدی. | تدوین زمان‌بندی و بودجه پروژه‌های احیای محیط‌زیست. | تدوین برنامه‌های مدیریت منابع طبیعی، با به‌کارگیری دانش برنامه‌ریزی محیط‌زیستی یا الزامات نظارتی محیط‌زیستی ایالتی و فدرال. | شناسایی گزینه‌های جایگزین برای کاهش اثرات محیط‌زیستی، با اطمینان از رعایت استانداردها، قوانین یا مقررات مربوطه. | شناسایی اثرات کوتاه‌مدت و بلندمدت فعالیت‌های پاک‌سازی محیط‌زیستی. | بازرسی محل‌های فعال پاک‌سازی برای اطمینان از رعایت سیاست‌ها، استانداردها یا مقررات محیط‌زیستی و ایمنی. | اطلاع‌رسانی به نهادهای نظارتی یا صادرکننده مجوز درباره انحراف از برنامه‌های پاک‌سازی اجراشده. | برنامه‌ریزی پروژه‌های احیای محیط‌زیست، با استفاده از پایگاه‌های داده زیستی، راهبردهای محیط‌زیستی و نرم‌افزارهای برنامه‌ریزی. | برنامه‌ریزی یا سرپرستی مطالعات محیط‌زیستی برای دستیابی به انطباق با مقررات محیط‌زیستی در ساخت، اصلاح، بهره‌برداری، تملک یا واگذاری تأسیساتی مانند نیروگاه‌ها. | ارائه راهبری فنی در زمینه برنامه‌ریزی محیط‌زیستی به مهندسان انرژی، زیست‌شناسان، زمین‌شناسان یا سایر متخصصانی که برنامه‌ها یا راهبردهای احیا را تدوین می‌کنند. | بازبینی طرح‌های موجود پاک‌سازی محیط‌زیستی. | سرپرستی و ارائه راهنمایی فنی، آموزش یا کمک به کارکنان میدانی که در احیای زیستگاه‌ها فعالیت می‌کنند. | نگارش درخواست‌های اعطای اعتبار برای تأمین مالی پروژه‌های احیا.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | شنیدن فعال | تفکر انتقادی | علوم پایه | یادگیری فعال | ریاضیات | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست و بهداشت | متخصصان پایداری زیست‌محیطی</t>
+          <t>مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کارشناسان پایداری و توسعه پایدار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>تحلیل تغییرات سامانه‌ها به‌منظور بهبود عملکرد زیست‌محیطی صنایع و پیشگیری از پیامدهای نامطلوب | به‌کارگیری یافته‌های مربوط به اکوسیستم‌های طبیعی در تحلیل سامانه‌های صنعتی و اقتصادی | اجرای ارزیابی‌های پایداری زیست‌محیطی با استفاده از روش‌های تحلیل جریان مواد و جریان ترکیبات | بازطراحی فرایندهای صنعتی خطی به چرخه‌های بسته و چرخشی جهت بازیافت و تبدیل ضایعات به مواد اولیه | مدل‌سازی پیچیده و پویای ریاضی برای تحلیل اثرات بوم‌شناختی و صنعتی | بررسی جریان محلی، منطقه‌ای و جهانی مواد و انرژی در فرآیندهای تولید صنعتی | شناسایی پیامدهای زیست‌محیطی کالاها، خدمات، طرح‌ها و پروژه‌های صنعتی | ارائه راهکارهای پایش و کاهش انتشار آلاینده‌ها و پسماندهای صنایع | تهیه گزارش‌های ارزیابی اثرات زیست‌محیطی EIA و ارائه به سازمان‌های ذی‌ربط و صنایع | ارائه مشاوره‌های فنی به مدیران صنایع در خصوص انطباق با الزامات و استانداردهای محیط زیست</t>
+          <t>تجزیه و تحلیل تغییرات طراحی‌شده برای بهبود عملکرد محیط‌زیستی سامانه‌های پیچیده و پرهیز از پیامدهای منفی ناخواسته. | به‌کارگیری پژوهش‌های جدید یا موجود درباره بوم‌سازگان‌های طبیعی برای درک سامانه‌های اقتصادی و صنعتی در بستر محیط‌زیست. | ساخت و نگهداری پایگاه‌های داده اطلاعات مربوط به گزینه‌های جایگزین انرژی، آلاینده‌ها، محیط‌های طبیعی، فرایندهای صنعتی و سایر اطلاعات مرتبط با تغییرات بوم‌شناختی. | انجام ارزیابی‌های محیط‌زیستی مطابق با استانداردها، مقررات یا قوانین مربوطه. | انجام تحلیل‌هایی برای تعیین بیشینه کاری که با مقدار معینی انرژی در یک سامانه انجام‌شدنی است، مانند سامانه‌های تولید صنعتی و سامانه‌های تصفیه پسماند. | انجام پژوهش کاربردی درباره آثار فرایندهای صنعتی بر حفاظت، احیا، سیاهه‌برداری، پایش یا بازمعرفی گونه‌ها به محیط طبیعی. | انجام ارزیابی‌های پایداری محیط‌زیستی، با استفاده از فنون تحلیل جریان مواد (MFA) یا تحلیل جریان ماده (SFA). | اجرای پروژه‌های علمی حفاظت، کاهش اثر یا احیا برای پیشگیری از آسیب به منابع، حفظ یکپارچگی زیستگاه‌های حساس و کمینه‌سازی اثر فعالیت‌های انسانی. | ساخت مدل‌های ریاضی پیچیده و پویا از جمعیت، اجتماع زیستی یا سامانه‌های بوم‌شناختی. | تدوین سناریوهای سرمایه‌گذاری در انرژی‌های جایگزین برای مقایسه هزینه‌ها و منافع اقتصادی و محیط‌زیستی. | تدوین یا آزمون پروتکل‌هایی برای پایش اجزای بوم‌سازگان و فرایندهای بوم‌شناختی. | ارزیابی اثربخشی برنامه‌های بوم‌شناسی صنعتی، با استفاده از تحلیل و کاربردهای آماری. | بررسی مصرف و جریان محلی، منطقه‌ای یا جهانی مواد و انرژی در فرایندهای تولید صنعتی. | بررسی مسائل اجتماعی و رابطه آن‌ها با سامانه‌های فنی و محیط‌زیست. | پیش‌بینی وضعیت یا شرایط آینده بوم‌سازگان‌ها، بر پایه تغییر شیوه‌های صنعتی یا شرایط محیط‌زیستی. | شناسایی اثرات محیط‌زیستی ناشی از محصولات، سامانه‌ها یا پروژه‌ها. | شناسایی یا مقایسه اجزای تشکیل‌دهنده یا روابط میان اجزای سامانه‌های صنعتی، اجتماعی و طبیعی. | شناسایی یا تدوین راهبردها یا روش‌هایی برای کمینه‌سازی اثر محیط‌زیستی فرایندهای تولید صنعتی. | شناسایی گزینه‌های پایدار جایگزین برای شیوه‌های صنعتی یا مدیریت پسماند. | بررسی حوادث اثرگذار بر محیط‌زیست برای ارزیابی پیامدهای بوم‌شناختی. | بررسی سازگاری گونه‌های مختلف جانوری و گیاهی با شرایط محیط‌زیستی تغییریافته. | بررسی اثر تغییر مدیریت یا کاربری اراضی بر بوم‌سازگان‌ها. | پایش اثر محیط‌زیستی فعالیت‌های توسعه، آلودگی یا تخریب اراضی. | انجام تحلیل‌هایی برای تعیین اینکه رفتار انسان چگونه بر تغییرات محیط‌زیست اثر می‌گذارد و از آن اثر می‌پذیرد. | انجام تحلیل‌های داده‌ستانده با گسترش محیط‌زیستی (EE I-O). | برنامه‌ریزی یا انجام پژوهش میدانی در موضوعاتی مانند تولید صنعتی، بوم‌شناسی صنعتی، بوم‌شناسی جمعیت و تولید یا پایداری محیط‌زیستی. | برنامه‌ریزی یا انجام مطالعاتی درباره پیامدهای بوم‌شناختی تغییرات تاریخی یا پیش‌بینی‌شده در فرایندهای صنعتی یا توسعه. | تهیه برنامه‌هایی برای مدیریت منابع تجدیدپذیر. | تهیه گزارش‌های فنی و پژوهشی، مانند گزارش‌های ارزیابی اثرات محیط‌زیستی، و انتقال نتایج به افراد فعال در صنعت، دولت یا عموم مردم. | ترویج استفاده از سامانه‌های مدیریت محیط‌زیست (EMS) برای کاهش پسماند یا بهبود استفاده محیط‌زیست‌سازگار از منابع طبیعی. | ارائه مواد فنی درباره مسائل محیط‌زیستی، دستورالعمل‌های نظارتی یا اقدامات انطباق به مدیران صنعتی. | پیشنهاد روش‌هایی برای حفاظت از محیط‌زیست یا کمینه‌سازی آسیب محیط‌زیستی ناشی از شیوه‌های تولید صنعتی. | بازطراحی سامانه‌های خطی یا حلقه‌باز به سامانه‌های چرخه‌ای یا حلقه‌بسته، به‌گونه‌ای که پسماندها به ورودی فرایندهای جدید تبدیل شوند و از بوم‌سازگان‌های طبیعی الگو بگیرند. | پژوهش درباره آثار محیط‌زیستی کاربری زمین و آب برای تعیین روش‌های بهبود شرایط محیط‌زیستی یا افزایش ستانده‌ها، مانند عملکرد محصولات کشاورزی. | پژوهش درباره منابع آلودگی برای تعیین اثر محیط‌زیستی یا تدوین روش‌های کاهش و کنترل آلودگی. | بازبینی شیوه‌های صنعتی، مانند روش‌ها و مواد به‌کاررفته در ساخت یا تولید، برای شناسایی مسئولیت‌های احتمالی و مخاطرات محیط‌زیستی. | بازبینی ادبیات پژوهشی برای به‌روز نگه‌داشتن دانش در موضوعات مرتبط با بوم‌شناسی صنعتی، مانند علوم فیزیکی، فناوری، اقتصاد و سیاست‌گذاری عمومی. | برگردان نظریه‌های بوم‌شناسی صنعتی به شیوه‌های اجرایی بوم‌صنعتی.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | علوم پایه | سخن گفتن | شنیدن فعال | نگارش | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>دانشمندان علوم جوی و فضایی | جغرافیدانان | تکنسین‌های زمین‌شناسی به استثنای آب‌شناسی | آب‌شناسان و هیدرولوژیست‌ها | مهندسان معدن و زمین‌شناسی از جمله ایمنی معدن | مهندسان نفت | نقشه‌برداران</t>
+          <t>دانشمندان و کارشناسان علوم جوی و فضا | جغرافیدانان | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | آب‌شناسان و هیدرولوژیست‌ها | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | مهندسان نفت | مهندسان نقشه‌برداری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>تحلیل و تفسیر داده‌های زمین‌شناسی، ژئوشیمیایی و ژئوفیزیکی حاصل از لاگ‌های چاه، مغزه‌گیری و تصاویر هوایی | برنامه‌ریزی و اجرای مطالعات میدانی، پیمایش‌های ژئوفیزیکی و عملیات حفاری اکتشافی | شناسایی و تخمین ذخایر احتمالی نفت، گاز، کانسارهای معدنی و مصالح ساختمانی | تهیه نقشه‌ها، مقاطع ساختاری، نمودارها و گزارش‌های تخصصی زمین‌شناسی | اندازه‌گیری ویژگی‌های زمین‌فیزیکی شامل گرانش و میدان‌های مغناطیسی با دستگاه‌های تخصصی | ارائه مشاوره در ساخت پروژه‌های عمرانی سدسازی، راه‌سازی، فونداسیون و پایدارسازی شیب‌ها | شناسایی و ارزیابی مخاطرات طبیعی نظیر رانش زمین، فرونشست، زلزله و فوران‌های آتشفشانی | آزمایش و آنالیز سنگ‌ها، کانی‌ها و خاک‌ها در آزمایشگاه به‌منظور تعیین ویژگی‌های پتروفیزیکی و کانی‌شناسی | بررسی وضعیت هیدروژئولوژی جهت مکان‌یابی دفن پسماند و بهسازی سایت‌های آلوده | ارائه توصیه‌های تخصصی پیرامون مکان‌یابی ایمن سازه‌های حساس و تاسیسات زیربنایی</t>
+          <t>ارائه مشاوره به شرکت‌های ساختمانی یا نهادهای دولتی درباره ساخت سد یا جاده، طراحی پی، کاربری زمین یا مدیریت منابع. | تجزیه و تحلیل و تفسیر داده‌های زمین‌شناسی، با استفاده از نرم‌افزارهای رایانه‌ای. | تجزیه و تحلیل و تفسیر اطلاعات زمین‌شناسی، ژئوشیمیایی یا ژئوفیزیکی از منابعی مانند داده‌های نقشه‌برداری، نگارهای چاه، گمانه‌ها یا عکس‌های هوایی. | ارزیابی حرکت آب‌های زیرزمینی یا سطحی برای ارائه مشاوره در موضوعاتی مانند مدیریت پسماند، انتخاب مسیر و محل، یا احیای محل‌های آلوده. | همکاری با پژوهشگران پزشکی یا سلامت برای رسیدگی به مشکلات سلامت مرتبط با مواد یا فرایندهای زمین‌شناختی. | انتقال یافته‌های زمین‌شناختی از راه نگارش مقالات پژوهشی، شرکت در همایش‌ها یا تدریس علوم زمین در دانشگاه‌ها. | انجام مطالعات زمین‌شناسی یا ژئوفیزیکی برای فراهم کردن اطلاعات مورد استفاده در توسعه منطقه‌ای، انتخاب محل یا اجرای پروژه‌های عمرانی. | طراحی نقشه‌های زمین‌شناسی معدن، پایش یکپارچگی سازه‌ای معدن، یا مشاوره و نظارت بر گروه‌های معدن‌کاری. | تعیین روش‌های وارد کردن ژئومتان یا هیدرات‌های متان به تولید جهانی انرژی یا ارزیابی پیامدهای محیط‌زیستی احتمالی این کار. | تعیین راه‌های کاهش پیامدهای منفی پراکنش گردوغبار معدنی. | توسعه نرم‌افزارهای کاربردی برای تجزیه و تحلیل و تفسیر داده‌های زمین‌شناسی. | تدوین راهبردهایی برای استخراج و احیای منابع با سازگاری بیشتر با محیط‌زیست. | تدوین روش‌هایی برای مهار یا استفاده از گازهایی که در فرایند تولید نفت به‌صورت پسماند سوزانده می‌شوند. | شناسایی ذخایر مصالح ساختمانی مناسب برای استفاده به‌عنوان سنگدانه بتن، خاکریز جاده یا سایر کاربردها. | شناسایی منابع جدید عناصر گروه پلاتین برای کاربردهای صنعتی، مانند پیل‌های سوختی خودرو یا سامانه‌های کاهش آلودگی. | شناسایی محل‌های ممکن برای پروژه‌های ترسیب کربن. | شناسایی مخاطرات بلایای طبیعی، مانند رانش زمین، زمین‌لرزه یا فوران آتشفشان. | بازرسی پروژه‌های ساختمانی برای تحلیل مسائل مهندسی، با استفاده از تجهیزات آزمون یا ماشین‌آلات حفاری. | بررسی ترکیب، ساختار یا تاریخچه پوسته زمین از راه گردآوری، بررسی، اندازه‌گیری یا طبقه‌بندی خاک‌ها، کانی‌ها، سنگ‌ها یا بقایای فسیلی. | مکان‌یابی و برآورد ذخایر احتمالی گاز طبیعی، نفت یا کانه‌های معدنی یا منابع آب زیرزمینی، با استفاده از عکس‌های هوایی، نمودارها یا نتایج پژوهش و نقشه‌برداری. | یافتن و بازبینی مقالات پژوهشی یا گزارش‌های محیط‌زیستی، تاریخی یا فنی. | مکان‌یابی منابع بالقوه انرژی زمین‌گرمایی. | اندازه‌گیری ویژگی‌های زمین، مانند گرانش یا میدان‌های مغناطیسی، با استفاده از تجهیزاتی مانند لرزه‌نگار، گرانی‌سنج، ترازوی پیچشی یا مغناطیس‌سنج. | برنامه‌ریزی یا انجام مطالعات و نقشه‌برداری‌های میدانی زمین‌شناسی، ژئوشیمیایی یا ژئوفیزیکی، نمونه‌برداری، یا برنامه‌های حفاری و آزمون که برای گردآوری داده‌های پژوهشی یا کاربردی به کار می‌روند. | تهیه نقشه‌های زمین‌شناسی، نمودارهای مقطعی، چارت‌ها یا گزارش‌های مربوط به استخراج مواد معدنی، کاربری زمین یا مدیریت منابع، با استفاده از نتایج کار میدانی یا پژوهش آزمایشگاهی. | ارائه مشاوره درباره مکان‌یابی ایمن پروژه‌های راکتور هسته‌ای جدید یا روش‌های مدیریت پسماند هسته‌ای. | پژوهش درباره فرایندهای ژئومکانیکی یا ژئوشیمیایی برای استفاده در پروژه‌های ترسیب کربن. | پژوهش درباره راه‌های کاهش ردپای بوم‌شناختی کلان‌شهرهایی که روزبه‌روز فراگیرتر می‌شوند. | بازبینی گزارش‌ها و انتشارات محیط‌زیستی، تاریخی یا فنی از نظر صحت. | بازبینی برنامه‌های کاری برای تعیین اثربخشی فعالیت‌های کاهش آلودگی خاک یا آب زیرزمینی. | مطالعه شاخص‌های تاریخی تغییر اقلیم موجود در مکان‌هایی مانند پوشش‌های یخی یا سازندهای سنگی برای تدوین مدل‌های تغییر اقلیم. | آزمون الماس‌ها یا ساینده‌های صنعتی، خاک یا سنگ برای تعیین ویژگی‌های زمین‌شناختی آن‌ها، با استفاده از ابزارهای نوری، پرتو ایکس، حرارتی، اسیدی یا دقیق.</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم پایه | درک مطلب | شنیدن فعال | سخن گفتن | ریاضیات | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | علوم | درک مطلب | گوش دادن فعال | سخن گفتن | ریاضیات | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دانشمندان حفاظت از منابع طبیعی | مهندسان محیط زیست | تکنسین‌های زمین‌شناسی به استثنای آب‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های هیدرولوژی و آب‌شناسی | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
+          <t>دانشمندان حفاظت از منابع طبیعی | مهندسان محیط‌زیست | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>طراحی و اجرای مطالعات هیدروژئولوژیکی برای مدیریت بهینه و پایدار منابع آب سطحی و زیرزمینی | توسعه و پیاده‌سازی مدل‌های رقومی برای پیش‌بینی هیدرولوژیکی، سیلاب و بیلان آب | اندازه‌گیری، ثبت و تحلیل دبی جریان رودخانه‌ها، تراز آب‌های زیرزمینی و کیفیت منابع آب | نمونه‌برداری از منابع آب در مطالعات میدانی و سنجش داده‌های ایستگاه‌های پایش آنلاین | ارزیابی داده‌های هیدرولوژیکی به‌منظور امکان‌سنجی پروژه‌های سدسازی، شبکه‌های آبیاری و سامانه‌های هشدار سیل | مطالعه مخاطرات منابع آب شهری و روستایی شامل دوره‌های خشکسالی، طغیان سیلاب و افت تراز سفره‌ها | نصب، نگهداری و کالیبراسیون تجهیزات هیدرومتری، باران‌سنجی و رسوب‌سنجی | بررسی و حل اختلافات حقوقی و کارشناسی مربوط به حریم، بستر و برداشت از منابع آب عمومی | تهیه گزارش‌های تخصصی، اطلس‌های هیدرولوژی و نقشه‌های پهنه‌بندی حوضه‌های آبخیز | ارزیابی اثرات هیدروژئولوژیکی سایت‌های دفع پسماند و کانون‌های آلاینده بر آبخوان‌ها</t>
+          <t>اداره برنامه‌هایی که برای اطمینان از مسدودسازی صحیح چاه‌های متروکه طراحی شده‌اند. | پاسخ‌گویی به پرسش‌ها و ارائه کمک و اطلاعات فنی به پیمانکاران یا عموم مردم درباره موضوعاتی مانند حفر چاه، الزامات آیین‌نامه‌ای، آب‌شناسی و زمین‌شناسی. | به‌کارگیری یافته‌های پژوهشی برای کمک به کمینه‌سازی اثرات محیط‌زیستی آلودگی، بیماری‌های منتقله از آب، فرسایش و رسوب‌گذاری. | گردآوری و تجزیه و تحلیل نمونه‌های آب در چارچوب بررسی‌های میدانی یا برای اعتبارسنجی داده‌های پایشگرهای خودکار. | گردآوری و ارزیابی اطلاعات آب‌شناختی برای تهیه نقشه‌ها و چارت‌های ناوبری و پیش‌بینی شرایط جوی. | انجام پژوهش و انتقال اطلاعات برای ترویج حفاظت و صیانت از منابع آب. | انجام ارزیابی‌های اقلیمی کوتاه‌مدت و بلندمدت و مطالعه رخداد توفان‌ها. | هماهنگی و سرپرستی کار کارکنان متخصص و فنی، از جمله دستیاران پژوهشی، تکنولوژیست‌ها و تکنسین‌ها. | طراحی و انجام بررسی‌های علمی هیدروژئولوژیکی برای اطمینان از در دسترس بودن اطلاعات دقیق و مناسب جهت استفاده در تصمیم‌های مدیریت منابع آب. | طراحی سازه‌های عمرانی مرتبط با فعالیت‌های آب‌نگاری و سرپرستی ساخت، نصب و نگهداری آن‌ها. | تدوین مدل‌های رایانه‌ای برای پیش‌بینی‌های آب‌شناختی. | تدوین یا اصلاح روش‌های انجام مطالعات آب‌شناختی. | ارزیابی داده‌ها و ارائه توصیه درباره امکان‌پذیری پروژه‌های شهری، مانند نیروگاه‌های برق‌آبی، سامانه‌های آبیاری، سامانه‌های هشدار سیل و تأسیسات تصفیه پسماند. | ارزیابی داده‌های پژوهشی از نظر اثر آن‌ها بر موضوعاتی مانند حفاظت خاک و آب، برنامه‌ریزی مهار سیل و پیش‌بینی تأمین آب. | نصب، نگهداری و کالیبراسیون ابزارهایی مانند دستگاه‌های پایش تراز آب، بارش و رسوب. | بررسی شکایت‌ها یا اختلافات مرتبط با تغییر در آب‌های عمومی، شامل گردآوری اطلاعات، پیشنهاد گزینه‌های جایگزین، آگاه‌سازی طرف‌ها از پیشرفت کار و تهیه پیش‌نویس دستورها. | بررسی ویژگی‌ها، خاستگاه و رفتار یخچال‌های طبیعی، یخ، برف و خاک‌های همیشه‌یخ. | اندازه‌گیری و ترسیم نمودار پدیده‌هایی مانند تراز دریاچه‌ها، دبی رودخانه‌ها و تغییرات حجم آب. | پایش کار پیمانکاران حفر چاه، حفاران اکتشافی و مهندسان و اعمال مقررات مربوط به فعالیت آنان. | تهیه ارزیابی‌های هیدروژئولوژیکی محل‌های شناخته‌شده یا مظنون به پسماند خطرناک و تأسیسات تصفیه زمینی و دامداری‌های متمرکز. | تهیه گزارش‌های کتبی و شفاهی برای تشریح نتایج پژوهش، با استفاده از تصاویر، نقشه‌ها، پیوست‌ها و سایر اطلاعات. | بازبینی درخواست‌های طرح‌های مکانی و مجوزها و ارائه توصیه درباره تأیید، رد، اصلاح یا انجام بررسی بیشتر. | مطالعه و تجزیه و تحلیل جنبه‌های فیزیکی زمین از نظر مؤلفه‌های آب‌شناختی، شامل جو، آب‌کره و ساختار درونی. | مطالعه و مستندسازی مقدار، توزیع، وضعیت و توسعه آب‌های زیرزمینی و سطحی. | مطالعه مسائل تأمین آب عمومی، از جمله خطر سیل و خشک‌سالی، کیفیت آب، فاضلاب و اثرات آن بر زیستگاه‌های تالابی.</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم پایه | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>شیمی‌دانان | دانشمندان علوم مواد | فیزیک‌دانان | دانشمندان علوم جوی و فضایی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | دانشمندان و متخصصان محیط زیست و بهداشت</t>
+          <t>شیمی‌دانان | کارشناسان و دانشمندان علوم مواد | فیزیک‌دانان | دانشمندان و کارشناسان علوم جوی و فضا | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | کارشناسان و متخصصان علوم محیطی (شامل بهداشت)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>انجام پژوهش‌های بنیادین و کاربردی در شاخه‌های تخصصی علوم فیزیکی | طراحی و اجرای آزمایش‌های تخصصی جهت بررسی پدیده‌های فیزیکی و شیمیایی | کار با تجهیزات و ابزارهای پیشرفته آزمایشگاهی برای سنجش فرآیندها و خواص فیزیکی | تدوین مدل‌های ریاضی و محاسباتی برای شبیه‌سازی سامانه‌های فیزیکی | تحلیل و اعتبارسنجی داده‌های تجربی و مشاهداتی و محاسبه عدم قطعیت در اندازه‌گیری‌ها | نگارش گزارش‌های فنی، مقالات علمی-پژوهشی و پروپوزال‌های دریافت اعتبار پژوهشی | کالیبراسیون، نگهداری و کنترل عملکرد ابزارهای دقیق آزمایشگاهی و میدانی | نظارت بر فعالیت تکنسین‌های آزمایشگاه و هماهنگی عملیات کارگاهی و صحرایی | حصول اطمینان از رعایت دقیق شیوه‌نامه‌های ایمنی در مواجهه با مواد خطرناک و پرتوها | مستندسازی و ثبت دقیق داده‌ها، روش‌ها، نتایج آزمون‌ها و فرآیندهای کالیبراسیون</t>
+          <t>انجام پژوهش در تخصص‌های علوم فیزیکی که جداگانه طبقه‌بندی نشده‌اند. | طراحی و انجام آزمایش برای بررسی پدیده‌های فیزیکی و شیمیایی. | کار با ابزارهای دقیق تخصصی برای اندازه‌گیری خواص و فرایندهای فیزیکی. | تدوین مدل‌های ریاضی و محاسباتی سامانه‌های فیزیکی. | تجزیه و تحلیل داده‌های آزمایشی و مشاهده‌ای و کمّی‌سازی عدم قطعیت اندازه‌گیری. | تهیه گزارش‌های پژوهشی، مقالات فنی و پیشنهادهای دریافت اعتبار مالی. | تفسیر یافته‌ها و ارائه مشاوره درباره کاربردهای صنعتی یا محیط‌زیستی آن‌ها. | کالیبراسیون و نگهداری تجهیزات علمی و راستی‌آزمایی عملکرد ابزارها. | گردآوری نمونه‌های میدانی و انجام اندازه‌گیری‌های محیط‌زیستی در شرایط گوناگون. | بازبینی ادبیات علمی و ارزیابی فنون اندازه‌گیری جدید. | سرپرستی تکنسین‌ها و هماهنگی عملیات آزمایشگاهی یا میدانی. | حصول اطمینان از رعایت رویه‌های ایمنی مربوط به مواد خطرناک و پرتوها. | ارائه یافته‌های فنی به مخاطبان علمی، نظارتی و مدیریتی. | نگهداری سوابق دقیق روش‌ها، کالیبراسیون‌ها و نتایج.</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | علوم پایه | شنیدن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دانشمندان علوم جوی و فضایی | کارتوگراف‌ها و فتوگرامتریست‌ها | نقشه‌برداران ژئودزی | کارشناسان و تکنسین‌های سامانه‌های اطلاعات جغرافیایی GIS | تکنسین‌های زمین‌شناسی به استثنای آب‌شناسی | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری</t>
+          <t>دانشمندان و کارشناسان علوم جوی و فضا | کارشناسان نقشه‌نگاری و فتوگرامتری | مهندسان نقشه‌برداری ژئودزی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>تحلیل تصاویر و داده‌های ماهواره‌ای، پهپادی و هوایی با استفاده از نرم‌افزارهای تخصصی پردازش تصویر و GIS | به‌کارگیری تکنیک‌های سنجش از دور در مدل‌سازی منابع آب، پوشش اراضی و پدیده‌های زیست‌محیطی | پردازش داده‌های اپتیک، راداری و لیدار و تولید نقشه‌های کاربری اراضی و مدل‌های رقومی ارتفاعی | توسعه الگوریتم‌ها و اسکریپت‌های خودکار جهت تصحیحات رادیومتریک، اتمسفری و هندسی تصاویر | طراحی و پیاده‌سازی پایگاه‌های داده مکانی برای آرشیو و بازیابی داده‌های سنجش از دور | ادغام و تلفیق داده‌های سنجش از دور با سایر لایه‌های مکانی و آمارهای توصیفی | نظارت کیفی بر فرآیند اخذ و پردازش داده‌های سنجنده‌ها جهت حفظ صحت خروجی‌ها | هدایت و نظارت بر نصب، راه‌اندازی و آزمون نرم‌افزارها و سامانه‌های سخت‌افزاری سنجش از دور | پایش تغییرات جنگل‌ها، منابع زیست‌محیطی و ذخایر کربن با به‌کارگیری داده‌های سری زمانی ماهواره‌ای | تهیه گزارش‌های تحلیلی، نقشه‌های موضوعی و ارائه خروجی‌های فنی به کارفرمایان و مدیران</t>
+          <t>تجزیه و تحلیل داده‌های به‌دست‌آمده از هواپیما، ماهواره یا سکوهای زمینی، با استفاده از نرم‌افزارهای تحلیل آماری، نرم‌افزارهای تحلیل تصویر یا سامانه‌های اطلاعات جغرافیایی (GIS). | به‌کارگیری داده‌ها یا فنون سنجش از دور، مانند مدل‌سازی آب‌های سطحی یا تشخیص توده‌های گردوغبار، برای رسیدگی به مسائل محیط‌زیستی. | شرکت در نشست‌ها یا سمینارها یا مطالعه ادبیات روز برای به‌روز نگه‌داشتن دانش تحولات حوزه سنجش از دور. | گردآوری داده‌های پشتیبان، مانند داده‌های اقلیمی یا برداشت میدانی، برای تأیید تحلیل‌های داده سنجش از دور. | گردآوری و قالب‌بندی داده‌های تصویری برای افزایش کارایی آن‌ها. | انجام پژوهش درباره کاربرد یا ارتقای فناوری سنجش از دور. | طراحی یا اجرای راهبردهای گردآوری، تجزیه و تحلیل یا نمایش داده‌های جغرافیایی. | تدوین روال‌های خودکار برای تصحیح آثار اعوجاج‌زا در تصویر، مانند پوشش گیاهی سطح زمین. | توسعه فنون تحلیلی یا سامانه‌های حسگر جدید. | تدوین یا ساخت پایگاه‌های داده برای اطلاعات پروژه‌های سنجش از دور یا پروژه‌های مکانی مرتبط. | هدایت همه فعالیت‌های مرتبط با استقرار، بهره‌برداری یا ارتقای سخت‌افزار و نرم‌افزار سنجش از دور. | هدایت نصب یا آزمون سخت‌افزار یا نرم‌افزار جدید سنجش از دور. | بحث درباره اهداف پروژه، الزامات تجهیزاتی یا روش‌شناسی با همکاران یا اعضای تیم. | یکپارچه‌سازی سایر منابع داده مکانی در پروژه‌ها. | مدیریت یا تجزیه و تحلیل داده‌های به‌دست‌آمده از سامانه‌های سنجش از دور برای دستیابی به نتایج معنادار. | پایش کیفیت عملیات گردآوری داده سنجش از دور برای تعیین لزوم تغییر در رویه‌ها یا تجهیزات. | سازماندهی و نگهداری داده‌های مکانی و مستندات مرتبط با آن‌ها. | مشارکت در کار میدانی. | تهیه یا ارائه گزارش‌ها یا ارائه‌های اطلاعات پروژه‌های مکانی. | پردازش تصاویر هوایی یا ماهواره‌ای برای تولید محصولاتی مانند نقشه‌های پوشش زمین. | پیشنهاد تهیه سخت‌افزار یا نرم‌افزار جدید سنجش از دور. | راه‌اندازی یا نگهداری سامانه‌های گردآوری داده سنجش از دور. | آموزش تکنسین‌ها در زمینه استفاده از فناوری سنجش از دور. | استفاده از داده‌های سنجش از دور در فعالیت‌های پایش جنگل یا کربن برای ارزیابی اثر تغییرات محیط‌زیستی.</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | دانشمندان داده | استادان علوم اقتصادی دانشگاه | اقتصاددانان محیط زیست | تحلیل‌گران مالی و سرمایه‌گذاری | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | آمارشناسان</t>
+          <t>تحلیل‌گران هوش تجاری | دانشمندان داده | استادان اقتصاد دانشگاه | اقتصاددانان محیط زیست | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>گردآوری، پردازش و تحلیل داده‌های اقتصادی جهت تبیین روندهای بازار با به‌کارگیری مدل‌های ریاضی و اقتصادسنجی | تدوین گزارش‌های پژوهشی، مقالات علمی و متون سیاستی در زمینه‌های مختلف اقتصادی | تدوین استانداردها و شاخص‌های اقتصادی و ارزیابی پیش‌بینی‌ها جهت فرمول‌بندی خط‌مشی‌ها | پیش‌بینی الگوهای تولید، مصرف، تورم، نرخ اشتغال و تعادل در بازارهای کالا و سرمایه | ارائه راهکارها و پیشنهادهای سیاستی جهت بهبود عملکرد اقتصادی، مالیاتی و پولی کشور | بررسی پیامدهای اقتصادی و اجتماعی لوایح قانونی، طرح‌های مالیاتی و سیاست‌های تنظیمی دولت | ارائه خدمات مشاوره‌ای و تحلیل‌های اقتصادی به بخش‌های دولتی، بنگاه‌های خصوصی و سازمان‌ها | پیش‌بینی روند تقاضا و مصرف منابع تجدیدپذیر و ارزیابی بهره‌برداری از ذخایر تجدیدناپذیر | ارائه نظرات کارشناسی تخصصی در مراجع تصمیم‌گیری و کمیسیون‌های نظارتی و قانون‌گذاری | تدریس مبانی، نظریه‌ها و روش‌های اقتصادسنجی و تحلیل داده‌های اقتصادی</t>
+          <t>گردآوری، تجزیه و تحلیل و گزارش داده‌ها برای تبیین پدیده‌های اقتصادی و پیش‌بینی روندهای بازار، با به‌کارگیری مدل‌های ریاضی و فنون آماری. | انجام پژوهش درباره مسائل اقتصادی و انتشار یافته‌های پژوهشی از راه گزارش‌های فنی یا مقالات علمی در نشریات. | تدوین دستورالعمل‌ها و استانداردهای اقتصادی و تهیه دیدگاه‌های مورد استفاده در پیش‌بینی روندها و تدوین سیاست اقتصادی. | تبیین اثر اقتصادی سیاست‌ها برای عموم مردم. | پیش‌بینی تولید و مصرف منابع تجدیدپذیر و عرضه، مصرف و تحلیل‌رفتن منابع تجدیدناپذیر. | تدوین توصیه‌ها، سیاست‌ها یا برنامه‌هایی برای حل مسائل اقتصادی یا تفسیر بازارها. | ارائه مشاوره و خدمات مشورتی درباره روابط اقتصادی به کسب‌وکارها، نهادهای دولتی و خصوصی و سایر کارفرمایان. | ارائه پشتیبانی در دعاوی حقوقی، مانند نگارش گزارش برای شهادت کارشناسی یا حضور به‌عنوان شاهد کارشناس. | بازبینی اسناد نگاشته‌شده به‌دست دیگران. | مطالعه داده‌های اقتصادی و آماری در حوزه تخصصی، مانند مالیه، کار یا کشاورزی. | مطالعه پیامدهای اجتماعی‌اقتصادی سیاست‌های عمومی جدید، مانند لوایح پیشنهادی، مالیات‌ها، خدمات و مقررات. | سرپرستی پروژه‌های پژوهشی و پروژه‌های مطالعاتی دانشجویان. | تدریس نظریه‌ها، اصول و روش‌های اقتصاد. | ادای شهادت در جلسات استماع نظارتی یا قانون‌گذاری درباره آثار برآوردی تغییرات قانون یا سیاست عمومی و ارائه توصیه بر پایه تحلیل هزینه‌فایده.</t>
         </is>
       </c>
     </row>
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | سخن گفتن | نظارت | استراتژی‌های یادگیری</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | سخن گفتن | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ریاضیات | اقتصاد و حسابداری | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | حقوق و مقررات دولتی</t>
+          <t>ریاضیات | اقتصاد و حسابداری | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال ریاضی | درک شفاهی | بیان شفاهی | بیان کتبی | محاسبات عددی | استدلال قیاسی</t>
+          <t>درک کتبی | استدلال ریاضی | درک شفاهی | بیان شفاهی | بیان کتبی | توانایی عددی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان | دانشمندان و متخصصان محیط زیست و بهداشت | بوم‌شناسان صنعتی | متخصصان پایداری زیست‌محیطی</t>
+          <t>مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | بوم‌شناسان صنعتی | کارشناسان پایداری و توسعه پایدار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ارزیابی اقتصادی هزینه‌-فایده فعالیت‌ها، طرح‌ها و مقررات اثرگذار بر محیط زیست و ذخایر منابع طبیعی | ارزش‌گذاری اقتصادی خدمات اکوسیستمی، منابع آب، کیفیت هوا و تنوع زیستی | مدل‌سازی اقتصادسنجی برای پیش‌بینی پیامدهای اقتصادی سیاست‌های اقلیمی و زیست‌محیطی | مقایسه تطبیقی آثار اقتصادی و زیست‌محیطی راهکارهای جایگزین در تولید انرژی و مصرف منابع | طراحی مشوق‌ها، ابزارهای مالیاتی و سیاست‌های مالی جهت ترویج توسعه پایدار و کاهش انتشار آلاینده‌ها | تدوین گزارش‌های ارزیابی اثرات اقتصادی و اجتماعی خط‌مشی‌ها برای ارائه به مراجع تصمیم‌گیر | پژوهش در خصوص هزینه‌های بلندمدت تخریب و احیای محیط زیست و پیامدهای اتمام منابع تجدیدناپذیر | طراحی و تدوین پروپوزال‌های پژوهشی جهت اخذ اعتبارات تحقیقاتی از نهادهای ذی‌ربط | نگارش مقالات علمی، گزارش‌های سیاستی و بسته‌های تحلیلی در حوزه اقتصاد محیط زیست | ارائه راهکارهای اقتصادی با رویکرد ارتقای بهره‌وری سبز و پایداری در کسب‌وکارها</t>
+          <t>ارزیابی هزینه‌ها و منافع فعالیت‌ها، سیاست‌ها یا مقررات گوناگونی که بر محیط‌زیست یا ذخایر منابع طبیعی اثر می‌گذارند. | گردآوری و تجزیه و تحلیل داده‌ها برای مقایسه پیامدهای محیط‌زیستی گزینه‌های سیاستی یا اجرایی اقتصادی. | انجام پژوهش در موضوعات اقتصادی و محیط‌زیستی، مانند استفاده از سوخت‌های جایگزین، کاربری اراضی عمومی و خصوصی، حفاظت خاک، کنترل آلودگی هوا و آب، و حفاظت از گونه‌های در معرض خطر. | انجام پژوهش برای مطالعه روابط میان مسائل محیط‌زیستی و الگوهای تولید و مصرف اقتصادی. | نشان دادن یا ترویج منافع اقتصادی مقررات محیط‌زیستی درست. | تدوین مدل‌ها، پیش‌بینی‌ها یا سناریوهای اقتصادی برای پیش‌بینی پیامدهای اقتصادی و محیط‌زیستی آینده. | تدوین برنامه‌های پروژه‌های پژوهشی محیط‌زیستی، شامل اطلاعات بودجه، اهداف، خروجی‌ها، زمان‌بندی و الزامات منابع. | تدوین برنامه‌ها یا توصیه‌های سیاستی برای دستیابی به اهداف محیط‌زیستی به شیوه‌های مقرون‌به‌صرفه. | تدوین برنامه‌ها یا توصیه‌های سیاستی برای ترویج پایداری و توسعه پایدار. | تدوین سامانه‌هایی برای گردآوری، تجزیه و تحلیل و تفسیر داده‌های محیط‌زیستی و اقتصادی. | بررسی پایان‌پذیری منابع طبیعی یا هزینه‌های بلندمدت بازسازی محیط‌زیست. | شناسایی و پیشنهاد شیوه‌های کسب‌وکار سازگار با محیط‌زیست. | تفسیر شاخص‌ها برای تشخیص سلامت کلی یک محیط. | پایش یا تجزیه و تحلیل روندهای بازار و محیط‌زیست. | انجام مدل‌سازی ریاضی پیچیده، پویا و یکپارچه سامانه‌های بوم‌شناختی، محیط‌زیستی یا اقتصادی. | تهیه و ارائه ارائه‌هایی برای انتقال نتایج مطالعات اقتصادی و محیط‌زیستی، طرح توصیه‌های سیاستی یا افزایش آگاهی از پیامدهای محیط‌زیستی. | تدریس دروس اقتصاد محیط‌زیست. | نگارش پیشنهادهای پژوهشی و درخواست‌های اعطای اعتبار برای دریافت تأمین مالی خصوصی یا عمومی مطالعات محیط‌زیستی و اقتصادی. | نگارش بیانیه‌های اثر اجتماعی، حقوقی یا اقتصادی برای آگاهی‌بخشی به تصمیم‌گیران درباره سیاست‌ها، استانداردها یا برنامه‌های منابع طبیعی. | نگارش اسناد فنی یا مقالات علمی برای انتقال نتایج مطالعات یا پیش‌بینی‌های اقتصادی.</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | نگارش | شنیدن فعال | درک مطلب | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری | نظارت</t>
+          <t>سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری | روان‌شناسی | ارتباطات و رسانه</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره | روان‌شناسی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | دانشمندان داده | مصاحبه‌گران به‌جز حوزه وام و اعتبارات | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | دستیاران پژوهشی علوم اجتماعی | آمارشناسان</t>
+          <t>تحلیل‌گران هوش تجاری | دانشمندان داده | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>طراحی پرسشنامه‌ها، شیوه‌نامه‌های مصاحبه و تعیین شاخص‌ها و ابزارهای گردآوری داده‌ها | تعیین روش‌های نمونه‌گیری، حجم نمونه و تدوین سازوکارهای وزن‌دهی آماری به داده‌ها | پردازش، پاک‌سازی و تحلیل آماری داده‌های حاصل از پیمایش‌ها و نظرسنجی‌ها با نرم‌افزارهای تخصصی | اجرای پیمایش‌ها از طریق مصاحبه‌های حضوری، پرسشنامه‌های برخط، گروه‌های کانون و نظرسنجی‌های تلفنی | نظارت بر عملکرد پرسشگران، مصاحبه‌گران و عوامل اجرایی جمع‌آوری اطلاعات و بازبینی خروجی‌ها | آموزش پرسشگران و تدوین شیوه‌نامه‌ها و راهنماهای اجرایی عملیات میدانی | پایش نرخ پاسخ‌گویی و تحلیل داده‌های مربوط به افت یا خطای پاسخ‌دهندگان | تهیه گزارش‌های تحلیلی، داشبوردها، جداول توصیفی و نمودارهای آماری از نتایج پیمایش‌ها | مستندسازی کامل متدولوژی، فرایند تدوین ابزارها و مراحل جمع‌آوری داده‌ها | تدوین پیشنهادهای پژوهشی و پروپوزال‌های تخصصی برای اجرای طرح‌های افکارسنجی و پیمایش بازار</t>
+          <t>تجزیه و تحلیل داده‌های حاصل از نظرسنجی‌ها، سوابق پیشین یا مطالعات موردی، با استفاده از نرم‌افزارهای آماری. | همکاری با سایر پژوهشگران در برنامه‌ریزی، اجرا و ارزیابی نظرسنجی‌ها. | انجام پژوهش برای گردآوری اطلاعات درباره موضوعات نظرسنجی. | اجرای نظرسنجی و گردآوری داده، با روش‌هایی مانند مصاحبه، پرسش‌نامه، گروه کانونی، نظرسنجی تحلیل بازار، نظرسنجی افکار عمومی، مرور ادبیات و بررسی پرونده‌ها. | رایزنی با کارفرمایان برای شناسایی نیازهای نظرسنجی و الزامات خاص، مانند نمونه‌های ویژه. | تعیین و تصریح جزئیات پروژه‌های نظرسنجی، شامل منابع اطلاعات، رویه‌های مورد استفاده و طراحی ابزارها و مواد نظرسنجی. | هدایت و بازبینی کار کارکنان، از جمله کارکنان پشتیبانی نظرسنجی و مصاحبه‌گرانی که داده‌ها را گردآوری می‌کنند. | هدایت به‌روزرسانی‌ها و تغییرات در اجرا و روش‌های نظرسنجی. | استخدام و آموزش جذب‌کنندگان و گردآورندگان داده. | پایش و ارزیابی پیشرفت و عملکرد نظرسنجی، با استفاده از گزارش‌های وضعیت نمونه و محاسبه نرخ پاسخ‌گویی. | تهیه و ارائه خلاصه‌ها و تحلیل‌های داده‌های نظرسنجی، شامل جدول‌ها، نمودارها و برگه‌های اطلاعاتی که فنون و نتایج نظرسنجی را تشریح می‌کنند. | تولید مستندات فرایند تدوین پرسش‌نامه، روش‌های گردآوری داده، طرح‌های نمونه‌گیری و تصمیم‌های مربوط به وزن‌دهی آماری نمونه. | بازبینی، طبقه‌بندی و ثبت داده‌های نظرسنجی برای آماده‌سازی تحلیل رایانه‌ای. | پشتیبانی، برنامه‌ریزی و هماهنگی عملیات یک یا چند نظرسنجی. | نگارش پیشنهادها برای کسب پروژه‌های جدید. | نگارش راهنماهای آموزشی برای استفاده مصاحبه‌گران نظرسنجی.</t>
         </is>
       </c>
     </row>
